--- a/StructureDefinition-ng-imm-organization.xlsx
+++ b/StructureDefinition-ng-imm-organization.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://dhin.org/2025Connectathon/StructureDefinition/ng-imm-organization</t>
+    <t>https://www.dhin-hie.org/IGs/StructureDefinition/ng-imm-organization</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-02T14:19:18+01:00</t>
+    <t>2025-09-10T08:54:29+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -764,7 +764,7 @@
     <t>Need to be able to track the kind of organization that this is - different organization types have different uses.</t>
   </si>
   <si>
-    <t>https://dhin.org/2025Connectathon/ValueSet/nigeria-facility-types</t>
+    <t>https://www.dhin-hie.org/IGs/ValueSet/nigeria-facility-types</t>
   </si>
   <si>
     <t>No equivalent in v2</t>
@@ -1180,7 +1180,7 @@
     <t>Madison</t>
   </si>
   <si>
-    <t>https://dhin.org/2025Connectathon/ValueSet/nigeria-lgas</t>
+    <t>https://www.dhin-hie.org/IGs/ValueSet/nigeria-lgas</t>
   </si>
   <si>
     <t>Address.district</t>
@@ -1205,7 +1205,7 @@
     <t>Sub-unit of a country with limited sovereignty in a federally organized country. A code may be used if codes are in common use (e.g. US 2 letter state codes).</t>
   </si>
   <si>
-    <t>https://dhin.org/2025Connectathon/ValueSet/nigeria-states</t>
+    <t>https://www.dhin-hie.org/IGs/ValueSet/nigeria-states</t>
   </si>
   <si>
     <t>Address.state</t>
@@ -1299,7 +1299,7 @@
     <t>Organization.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://dhin.org/2025Connectathon/StructureDefinition/ng-imm-organization)
+    <t xml:space="preserve">Reference(https://www.dhin-hie.org/IGs/StructureDefinition/ng-imm-organization)
 </t>
   </si>
   <si>
@@ -1790,7 +1790,7 @@
     <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="70.75" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="65.8359375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1805,7 +1805,7 @@
     <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="82.29296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="53.5625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="48.6484375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
